--- a/results/5er_crimelaw.xlsx
+++ b/results/5er_crimelaw.xlsx
@@ -445,13 +445,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>4.545454545454546</v>
+        <v>5.88235294117647</v>
       </c>
     </row>
     <row r="3">
@@ -464,10 +464,10 @@
         <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>64.28571428571429</v>
+        <v>7.142857142857142</v>
       </c>
     </row>
     <row r="4">
